--- a/output/pdf_financials_xlsx/CHP.UN.xlsx
+++ b/output/pdf_financials_xlsx/CHP.UN.xlsx
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -978,25 +978,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>14.224</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>11.551</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>20.079</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>27.36</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>41.414</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>52.593</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>41.892</v>
       </c>
     </row>
     <row r="13">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>67.148</v>
+        <v>66.824</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>199.614</v>
@@ -1763,25 +1763,25 @@
         <v>405.345</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>650.115</v>
+        <v>635.891</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-582.155</v>
+        <v>-593.706</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>22.329</v>
+        <v>2.25</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>744.136</v>
+        <v>716.776</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>796.692</v>
+        <v>755.278</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>783.3680000000001</v>
+        <v>730.775</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-59.244</v>
+        <v>-101.136</v>
       </c>
     </row>
     <row r="28">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>67.148</v>
+        <v>66.824</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>199.614</v>
@@ -1853,25 +1853,25 @@
         <v>405.345</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>650.115</v>
+        <v>635.891</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-582.155</v>
+        <v>-593.706</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>22.329</v>
+        <v>2.25</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>744.136</v>
+        <v>716.776</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>796.692</v>
+        <v>755.278</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>783.3680000000001</v>
+        <v>730.775</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-59.244</v>
+        <v>-101.136</v>
       </c>
     </row>
     <row r="30">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -44252,7 +44252,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -46886,7 +46886,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -50838,7 +50838,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -55904,7 +55904,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E663" s="5" t="n">

--- a/output/pdf_financials_xlsx/CHP.UN.xlsx
+++ b/output/pdf_financials_xlsx/CHP.UN.xlsx
@@ -1814,19 +1814,19 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1859,19 +1859,19 @@
         <v>-593.706</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>716.776</v>
+        <v>717.776</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>755.278</v>
+        <v>756.278</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>730.775</v>
+        <v>731.775</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-101.136</v>
+        <v>-100.136</v>
       </c>
     </row>
     <row r="30">
@@ -44674,7 +44674,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -44718,16 +44718,16 @@
         </is>
       </c>
       <c r="M513" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N513" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O513" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P513" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -47264,7 +47264,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -47303,10 +47303,10 @@
         </is>
       </c>
       <c r="L548" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M548" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N548" t="inlineStr">
         <is>
